--- a/artfynd/A 44628-2023 artfynd.xlsx
+++ b/artfynd/A 44628-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44628-2023 artfynd.xlsx
+++ b/artfynd/A 44628-2023 artfynd.xlsx
@@ -1728,7 +1728,7 @@
         <v>112795290</v>
       </c>
       <c r="B11" t="n">
-        <v>56753</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1767,14 +1767,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Äggfloten söder Tjåberget (Äggfloten söder Tjåberget), Dlr</t>
+          <t>Äggfloten söder Tjåberget, Äggfloten söder Tjåberget, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>475533</v>
+        <v>475534</v>
       </c>
       <c r="R11" t="n">
-        <v>6805901</v>
+        <v>6805902</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 44628-2023 artfynd.xlsx
+++ b/artfynd/A 44628-2023 artfynd.xlsx
@@ -1728,7 +1728,7 @@
         <v>112795290</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
